--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>31943.2</v>
+        <v>32027.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.33</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1369.189884269181</v>
+        <v>1369.279606669517</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.02567984387126176</v>
+        <v>0.02593672122377932</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04286326618088299</v>
+        <v>0.04275331338178709</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>30.27193754850471</v>
+        <v>30.37468848951173</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>31.88461156758171</v>
+        <v>31.91543684988383</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>18.36255319101313</v>
+        <v>18.36999529488321</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25141.82207848995</v>
+        <v>25153.65993189855</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.212920994812982</v>
+        <v>-0.214621834335904</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>22.66701192369646</v>
+        <v>22.67559896662348</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31035.44343253412</v>
+        <v>31049.2352340139</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.02841783438934997</v>
+        <v>-0.03054301126021897</v>
       </c>
     </row>
     <row r="15"/>
@@ -3922,7 +3922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4013,6 +4013,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>32027.45</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.674242424242</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0259367212238</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>32027.45</v>
+        <v>31948.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.39</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1369.279606669517</v>
+        <v>1369.412773253322</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.02593672122377932</v>
+        <v>0.02584551462642515</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04275331338178709</v>
+        <v>0.04286326618088299</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>30.37468848951173</v>
+        <v>30.33820585057006</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>31.91543684988383</v>
+        <v>31.90449205820132</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>18.36999529488321</v>
+        <v>18.36735290946272</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25153.65993189855</v>
+        <v>25152.48768506981</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.214621834335904</v>
+        <v>-0.212715263203484</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>22.67559896662348</v>
+        <v>22.67255006036907</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31049.2352340139</v>
+        <v>31048.07965489478</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.03054301126021897</v>
+        <v>-0.0281804517630061</v>
       </c>
     </row>
     <row r="15"/>
@@ -3922,7 +3922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4046,6 +4046,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>31948.4</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.674242424242</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0258455146264</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>31948.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>23.33</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.6742424242424242</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>1369.412773253322</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.02584551462642515</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>32.57575757575758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>30.33820585057006</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>31.90449205820132</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>18.36735290946272</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>25152.48768506981</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>-0.212715263203484</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>22.67255006036907</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>31048.07965489478</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>-0.0281804517630061</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.1958334707630009</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1698867137944766</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.231563965038343</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.02696917985100233</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1724407509749246</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.171974878292863</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,17 +857,17 @@
       <c r="B20" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.07927731426903128</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1399230240689016</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1709474782685572</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,17 +880,17 @@
       <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.04083625981713168</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>-0.01730270218714669</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1018197936706988</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -888,21 +903,20 @@
       <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.009852201380493586</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.2071796354631332</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1306071484006612</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1038,16 +1052,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>16331.4</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>33.75</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1057,16 +1071,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>17448.6</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>25.73</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1076,16 +1090,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>17666.05</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>24.11</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1095,16 +1109,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>17858.85</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>23.12</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1114,16 +1128,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>19038.2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>20.83</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1133,16 +1147,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>19717.65</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>21.01</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1152,16 +1166,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>19692.55</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>20.25</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1171,16 +1185,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>18870.6</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>18.01</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1190,16 +1204,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>19382.45</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>18.01</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1209,16 +1223,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>19496.85</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>17.92</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1228,16 +1242,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>18880.2</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>16.19</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1247,16 +1261,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>19445.6</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>19.34</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1266,16 +1280,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>19477.15</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>19.22</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1285,16 +1299,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>18789.9</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>18.09</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1304,16 +1318,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>17668.95</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>15.74</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1323,16 +1337,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>19585.55</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>17.55</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1342,16 +1356,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>20337.55</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>18.25</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1361,16 +1375,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>19707.05</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>17.62</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1380,16 +1394,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>20548.75</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>18.51</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1399,16 +1413,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>21266.05</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>20.17</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1418,16 +1432,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>20614.95</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>20.11</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1437,16 +1451,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>20244.15</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>19.43</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1456,16 +1470,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>19493.1</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>18.97</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1475,16 +1489,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>19618.6</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>19.21</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1494,16 +1508,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>20678.65</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>20.07</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1513,16 +1527,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>21498</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>21.02</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1532,16 +1546,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>22442.8</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>21.35</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1551,16 +1565,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>23128.8</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>20.29</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1570,16 +1584,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>22716.65</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>19.58</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1589,16 +1603,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>23566.35</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>20.41</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1608,16 +1622,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>23007.35</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>18.54</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1627,16 +1641,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>24755.15</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>19.89</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1646,16 +1660,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>26755.15</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>22.01</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1665,16 +1679,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>27125.3</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>21.76</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1684,16 +1698,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>27721.4</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>22.58</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1703,16 +1717,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>28146</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>22.89</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1722,16 +1736,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>28447.45</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>22.45</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1741,16 +1755,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>28493.3</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>21.82</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1760,16 +1774,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>30256.4</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>23.15</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1779,16 +1793,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>31940.45</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>24.86</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1798,16 +1812,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>32469.95</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>25.09</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1817,16 +1831,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>33349.9</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>25.58</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1836,16 +1850,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>30656.65</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>23.95</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1855,16 +1869,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>29910.2</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>22.88</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1874,16 +1888,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>29357.1</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>21.96</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1893,16 +1907,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>29429.95</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>21.75</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1912,16 +1926,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>27541.9</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>20.18</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1931,16 +1945,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>29215.85</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>22.28</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1950,16 +1964,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>30209.55</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>22.92</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1969,16 +1983,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>30907.3</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>24.29</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1988,16 +2002,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>32053.75</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>24.26</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2007,16 +2021,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>30995.9</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>23.47</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2026,16 +2040,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>31096.1</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>23.29</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2045,16 +2059,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>31553.9</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>23.77</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2064,16 +2078,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>32867.5</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>24.81</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2083,16 +2097,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>33216.25</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>24.68</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2102,16 +2116,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>33331</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>24.74</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2121,16 +2135,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>32701.65</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>24.46</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2140,16 +2154,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>33083.1</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>25.07</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2159,16 +2173,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>29556.95</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>22.93</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2178,16 +2192,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>32264.45</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>24.99</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2197,16 +2211,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>32390.95</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>24.71</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2216,16 +2230,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>32369.55</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>23.85</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2235,16 +2249,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>33391.95</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>24.37</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2254,16 +2268,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>32982.1</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>24.09</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2365,13 +2379,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>11615.79</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>23.37</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2379,12 +2393,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,C2)+1)/2)/COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2392,28 +2406,28 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16" t="n"/>
+      <c r="L2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>12135.81</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>25.35</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2421,12 +2435,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,C3)+1)/2)/COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2434,28 +2448,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>12919.07</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>25.67</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2463,12 +2477,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,C4)+1)/2)/COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2476,28 +2490,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>12047.3</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>23.24</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2505,12 +2519,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,C5)+1)/2)/COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2518,28 +2532,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>12349.25</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>23.26</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2547,15 +2561,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,C6)+1)/2)/COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2563,28 +2577,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>12273.75</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>21.98</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2592,15 +2606,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,C7)+1)/2)/COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2608,28 +2622,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>12100.85</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>21.07</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2637,15 +2651,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,C8)+1)/2)/COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2653,28 +2667,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>12785.85</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>22.67</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2682,15 +2696,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,C9)+1)/2)/COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2698,28 +2712,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>12624.25</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>20.4</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2727,15 +2741,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,C10)+1)/2)/COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2743,28 +2757,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>11770.9</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>20.47</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2772,15 +2786,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,C11)+1)/2)/COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2788,28 +2802,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>12427.2</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>22.22</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2817,15 +2831,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,C12)+1)/2)/COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2833,28 +2847,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>8592.200000000001</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>14.43</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2862,15 +2876,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,C13)+1)/2)/COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2878,28 +2892,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>10625.3</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>22.44</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2907,15 +2921,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,C14)+1)/2)/COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2923,28 +2937,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>11516.7</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>29.32</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2952,15 +2966,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,C15)+1)/2)/COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -2968,28 +2982,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>14616.65</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>36.21</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2997,15 +3011,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,C16)+1)/2)/COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3013,28 +3027,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>15999.3</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>33.32</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3042,15 +3056,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,C17)+1)/2)/COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3058,28 +3072,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>17666.05</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>24.11</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3087,15 +3101,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,C18)+1)/2)/COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3103,28 +3117,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>19717.65</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>21.01</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3132,15 +3146,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,C19)+1)/2)/COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3148,25 +3162,25 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>19382.45</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>18.01</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3174,15 +3188,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,C20)+1)/2)/COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3190,25 +3204,25 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>19445.6</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>19.34</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3216,15 +3230,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,C21)+1)/2)/COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3232,25 +3246,25 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>17668.95</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>15.74</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3258,15 +3272,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,C22)+1)/2)/COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3274,25 +3288,25 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>19707.05</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>17.62</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3300,15 +3314,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,C23)+1)/2)/COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3316,25 +3330,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>20614.95</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>20.11</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3342,15 +3356,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,C24)+1)/2)/COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3358,25 +3372,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>19618.6</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>19.21</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3384,15 +3398,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,C25)+1)/2)/COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3400,25 +3414,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>22442.8</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>21.35</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3426,15 +3440,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,C26)+1)/2)/COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3442,25 +3456,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>23566.35</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>20.41</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3468,15 +3482,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,C27)+1)/2)/COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3484,22 +3498,22 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>26755.15</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>22.01</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3507,15 +3521,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,C28)+1)/2)/COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3523,22 +3537,22 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>28146</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>22.89</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3546,15 +3560,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,C29)+1)/2)/COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3562,22 +3576,22 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>30256.4</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>23.15</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3585,15 +3599,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,C30)+1)/2)/COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3601,22 +3615,22 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>33349.9</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>25.58</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3624,15 +3638,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,C31)+1)/2)/COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3640,22 +3654,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>29357.1</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>21.96</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3663,15 +3677,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,C32)+1)/2)/COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3679,22 +3693,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>29215.85</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>22.28</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3702,15 +3716,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,C33)+1)/2)/COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3718,22 +3732,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>32053.75</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>24.26</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3741,15 +3755,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,C34)+1)/2)/COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3757,22 +3771,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>31553.9</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>23.77</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3780,15 +3794,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,C35)+1)/2)/COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3796,19 +3810,19 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>33331</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>24.74</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3816,15 +3830,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,C36)+1)/2)/COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3832,19 +3846,19 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="I36" s="30" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>29556.95</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>22.93</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3852,15 +3866,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,C37)+1)/2)/COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3868,19 +3882,19 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>32369.55</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>23.85</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3888,15 +3902,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,C38)+1)/2)/COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
@@ -3904,10 +3918,10 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="I38" s="30" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3984,30 +3998,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>31943.2</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>23.33</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.674242424242</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.0256798438713</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4017,30 +4031,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>32027.45</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>23.39</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.674242424242</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.0259367212238</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4050,30 +4064,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>31948.4</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>23.33</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.674242424242</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.0258455146264</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4193,4 +4207,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty50 Equal Weight Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4106,6 +4109,1112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty50 Equal Weight Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Asian Paints Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Axis Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bajaj Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bharat Electronics Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bharti Airtel Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cipla Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Coal India Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Eternal Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Grasim Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HCL Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HDFC Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hindalco Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ICICI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Infosys Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>InterGlobe Aviation Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ITC Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jio Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JSW Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Max Healthcare Institute Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nestle India Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NTPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Power Grid Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Reliance Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SBI Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Shriram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tata Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tata Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Titan Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Trent Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>UltraTech Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Wipro Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4207,43 +5316,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty50 Equal Weight Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31948.4</v>
+        <v>32135.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.33</v>
+        <v>23.47</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6742424242424242</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1369.412773253322</v>
+        <v>1369.19897741798</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02584551462642515</v>
+        <v>0.02561879819461166</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04286326618088299</v>
+        <v>0.0426075841499787</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>32.57575757575758</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>30.33820585057006</v>
+        <v>30.24751927784466</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>31.90449205820132</v>
+        <v>31.34698305608067</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.36735290946272</v>
+        <v>18.36078461055246</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25152.48768506981</v>
+        <v>25139.56751336022</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.212715263203484</v>
+        <v>-0.2176913246462521</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.67255006036907</v>
+        <v>22.66497125393416</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31048.07965489478</v>
+        <v>31032.85546409457</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.0281804517630061</v>
+        <v>-0.03430033004115207</v>
       </c>
     </row>
     <row r="16">
@@ -3939,7 +3939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4096,6 +4096,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>32135.1</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.681818181818</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.0256187981946</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>32135.1</v>
+        <v>31602.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.47</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6287878787878788</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1369.19897741798</v>
+        <v>1369.265597920278</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02561879819461166</v>
+        <v>0.02582168808209229</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0426075841499787</v>
+        <v>0.04332755632582323</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>31.81818181818182</v>
+        <v>37.12121212121212</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>30.24751927784466</v>
+        <v>30.32867523283691</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>31.34698305608067</v>
+        <v>35.08345105469956</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.36078461055246</v>
+        <v>18.36666262043547</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25139.56751336022</v>
+        <v>25148.83927477058</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2176913246462521</v>
+        <v>-0.2042173907956901</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.66497125393416</v>
+        <v>22.67175357302994</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31032.85546409457</v>
+        <v>31043.65221207603</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.03430033004115207</v>
+        <v>-0.01768832005936127</v>
       </c>
     </row>
     <row r="16">
@@ -3939,7 +3939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4129,6 +4129,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>31602.65</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.628787878788</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.0258216880821</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4169,7 +4202,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31602.65</v>
+        <v>31685.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.08</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6287878787878788</v>
+        <v>0.6439393939393939</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1369.265597920278</v>
+        <v>1369.28694900605</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02582168808209229</v>
+        <v>0.0256750780208439</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04332755632582323</v>
+        <v>0.0432152117545376</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>37.12121212121212</v>
+        <v>35.60606060606061</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>30.32867523283691</v>
+        <v>30.27003120833756</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>35.08345105469956</v>
+        <v>34.00525178674369</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.36666262043547</v>
+        <v>18.36241511751816</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25148.83927477058</v>
+        <v>25143.41537264901</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2042173907956901</v>
+        <v>-0.2064643423717303</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.67175357302994</v>
+        <v>22.66685260812535</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31043.65221207603</v>
+        <v>31037.42545134979</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.01768832005936127</v>
+        <v>-0.02044716473097019</v>
       </c>
     </row>
     <row r="16">
@@ -3939,7 +3939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4162,6 +4162,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>31685.3</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.643939393939</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.0256750780208</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4202,7 +4235,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31685.3</v>
+        <v>31241</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.14</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6439393939393939</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1369.28694900605</v>
+        <v>1369.018404907976</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0256750780208439</v>
+        <v>0.02568507714838431</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0432152117545376</v>
+        <v>0.04382120946538125</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>35.60606060606061</v>
+        <v>43.18181818181818</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>30.27003120833756</v>
+        <v>30.27403085935372</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>34.00525178674369</v>
+        <v>39.30948198507884</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.36241511751816</v>
+        <v>18.36270480652747</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25143.41537264901</v>
+        <v>25138.88084402826</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2064643423717303</v>
+        <v>-0.1953240663221965</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.66685260812535</v>
+        <v>22.64974949173965</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31037.42545134979</v>
+        <v>31007.92392074664</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.02044716473097019</v>
+        <v>-0.007460583184064506</v>
       </c>
     </row>
     <row r="16">
@@ -3939,7 +3939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4195,6 +4195,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>31241</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.568181818182</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.0256850771484</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4235,7 +4268,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31241</v>
+        <v>31139.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.82</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1369.018404907976</v>
+        <v>1369.38874230431</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02568507714838431</v>
+        <v>0.02581789012738733</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04382120946538125</v>
+        <v>0.04397537379067722</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>30.27403085935372</v>
+        <v>30.32715605095493</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>39.30948198507884</v>
+        <v>39.3254195425592</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.36270480652747</v>
+        <v>18.36655258826202</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25138.88084402826</v>
+        <v>25150.9503493061</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1953240663221965</v>
+        <v>-0.1923239846850473</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.64974949173965</v>
+        <v>22.62886752684256</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>31007.92392074664</v>
+        <v>30987.71644235377</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.007460583184064506</v>
+        <v>-0.004887092047380692</v>
       </c>
     </row>
     <row r="16">
@@ -3939,7 +3939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4228,6 +4228,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>31139.9</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.568181818182</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.0258178901274</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4268,7 +4301,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4538,17 +4571,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cipla Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4558,17 +4591,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coal India Ltd.</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4578,17 +4611,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Coal India Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4598,17 +4631,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4651,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4638,17 +4671,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4658,17 +4691,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -4678,17 +4711,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>HCL Technologies Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4731,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4718,17 +4751,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4738,17 +4771,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -4758,17 +4791,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4778,17 +4811,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4798,17 +4831,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Infosys Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -4818,17 +4851,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4838,17 +4871,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4858,17 +4891,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd.</t>
+          <t>Jio Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4911,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd.</t>
+          <t>JSW Steel Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -4898,17 +4931,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>Kotak Mahindra Bank Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4918,17 +4951,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4971,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4958,17 +4991,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4978,17 +5011,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4998,17 +5031,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTPC Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5051,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+          <t>NTPC Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5038,17 +5071,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5058,17 +5091,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5078,17 +5111,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5131,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5118,12 +5151,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5138,17 +5171,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5158,17 +5191,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5178,17 +5211,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5198,17 +5231,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Motors Passenger Vehicles Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5218,17 +5251,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5238,17 +5271,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5258,17 +5291,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Titan Company Ltd.</t>
+          <t>Tech Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5278,17 +5311,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5298,17 +5331,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5318,17 +5351,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wipro Ltd.</t>
+          <t>UltraTech Cement Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31139.9</v>
+        <v>30904.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.74</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5681818181818182</v>
+        <v>0.6567164179104478</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1369.38874230431</v>
+        <v>1329.223655913979</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.02581789012738733</v>
+        <v>0.001323015572568531</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04397537379067722</v>
+        <v>0.04301075268817205</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>43.18181818181818</v>
+        <v>34.32835820895522</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>30.32715605095493</v>
+        <v>20.52920622902741</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>39.3254195425592</v>
+        <v>30.18861261497688</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.36655258826202</v>
+        <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>25150.9503493061</v>
+        <v>23939.31804301076</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1923239846850473</v>
+        <v>-0.2253763440860214</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.62886752684256</v>
+        <v>22.29573297381295</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30987.71644235377</v>
+        <v>29636.01569473349</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.004887092047380692</v>
+        <v>-0.04104374306180858</v>
       </c>
     </row>
     <row r="16">
@@ -835,16 +835,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.02696917985100233</v>
+        <v>0.1015756321554483</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1724407509749246</v>
+        <v>0.170608927811255</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>0.171974878292863</v>
+        <v>0.1556701172555949</v>
       </c>
       <c r="F19" s="30" t="n"/>
       <c r="G19" s="30" t="n">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.07927731426903128</v>
+        <v>0.06130419264067477</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1399230240689016</v>
+        <v>0.1499984304707735</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.1709474782685572</v>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.04083625981713168</v>
+        <v>0.02226855881936141</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>-0.01730270218714669</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -967,7 +967,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2286,6 +2286,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>30904.45</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2402,7 +2421,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,C2)+1)/2)/COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$39,D2,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$39,D2,$C$2:$C$39,C2)+1)/2)/COUNTIFS($D$2:$D$39,D2,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2444,7 +2463,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,C3)+1)/2)/COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$39,D3,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$39,D3,$C$2:$C$39,C3)+1)/2)/COUNTIFS($D$2:$D$39,D3,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2486,7 +2505,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,C4)+1)/2)/COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$39,D4,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$39,D4,$C$2:$C$39,C4)+1)/2)/COUNTIFS($D$2:$D$39,D4,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2528,7 +2547,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,C5)+1)/2)/COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$39,D5,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$39,D5,$C$2:$C$39,C5)+1)/2)/COUNTIFS($D$2:$D$39,D5,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2573,7 +2592,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,C6)+1)/2)/COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$39,D6,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$39,D6,$C$2:$C$39,C6)+1)/2)/COUNTIFS($D$2:$D$39,D6,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2618,7 +2637,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,C7)+1)/2)/COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$39,D7,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$39,D7,$C$2:$C$39,C7)+1)/2)/COUNTIFS($D$2:$D$39,D7,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2663,7 +2682,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,C8)+1)/2)/COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$39,D8,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$39,D8,$C$2:$C$39,C8)+1)/2)/COUNTIFS($D$2:$D$39,D8,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2708,7 +2727,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,C9)+1)/2)/COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$39,D9,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$39,D9,$C$2:$C$39,C9)+1)/2)/COUNTIFS($D$2:$D$39,D9,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2753,7 +2772,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,C10)+1)/2)/COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$39,D10,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$39,D10,$C$2:$C$39,C10)+1)/2)/COUNTIFS($D$2:$D$39,D10,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2798,7 +2817,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,C11)+1)/2)/COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$39,D11,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$39,D11,$C$2:$C$39,C11)+1)/2)/COUNTIFS($D$2:$D$39,D11,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2843,7 +2862,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,C12)+1)/2)/COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$39,D12,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$39,D12,$C$2:$C$39,C12)+1)/2)/COUNTIFS($D$2:$D$39,D12,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2888,7 +2907,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,C13)+1)/2)/COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$39,D13,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$39,D13,$C$2:$C$39,C13)+1)/2)/COUNTIFS($D$2:$D$39,D13,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2933,7 +2952,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,C14)+1)/2)/COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$39,D14,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$39,D14,$C$2:$C$39,C14)+1)/2)/COUNTIFS($D$2:$D$39,D14,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2978,7 +2997,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,C15)+1)/2)/COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$39,D15,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$39,D15,$C$2:$C$39,C15)+1)/2)/COUNTIFS($D$2:$D$39,D15,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3023,7 +3042,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,C16)+1)/2)/COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$39,D16,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$39,D16,$C$2:$C$39,C16)+1)/2)/COUNTIFS($D$2:$D$39,D16,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3068,7 +3087,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,C17)+1)/2)/COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$39,D17,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$39,D17,$C$2:$C$39,C17)+1)/2)/COUNTIFS($D$2:$D$39,D17,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3113,7 +3132,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,C18)+1)/2)/COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$39,D18,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$39,D18,$C$2:$C$39,C18)+1)/2)/COUNTIFS($D$2:$D$39,D18,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3158,7 +3177,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,C19)+1)/2)/COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$39,D19,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$39,D19,$C$2:$C$39,C19)+1)/2)/COUNTIFS($D$2:$D$39,D19,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3173,7 +3192,10 @@
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="30" t="n"/>
+      <c r="K19" s="30">
+        <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
@@ -3200,7 +3222,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,C20)+1)/2)/COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$39,D20,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$39,D20,$C$2:$C$39,C20)+1)/2)/COUNTIFS($D$2:$D$39,D20,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3242,7 +3264,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,C21)+1)/2)/COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$39,D21,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$39,D21,$C$2:$C$39,C21)+1)/2)/COUNTIFS($D$2:$D$39,D21,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3284,7 +3306,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,C22)+1)/2)/COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$39,D22,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$39,D22,$C$2:$C$39,C22)+1)/2)/COUNTIFS($D$2:$D$39,D22,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3326,7 +3348,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,C23)+1)/2)/COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$39,D23,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$39,D23,$C$2:$C$39,C23)+1)/2)/COUNTIFS($D$2:$D$39,D23,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3368,7 +3390,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,C24)+1)/2)/COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$39,D24,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$39,D24,$C$2:$C$39,C24)+1)/2)/COUNTIFS($D$2:$D$39,D24,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3410,7 +3432,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,C25)+1)/2)/COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$39,D25,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$39,D25,$C$2:$C$39,C25)+1)/2)/COUNTIFS($D$2:$D$39,D25,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3452,7 +3474,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,C26)+1)/2)/COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$39,D26,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$39,D26,$C$2:$C$39,C26)+1)/2)/COUNTIFS($D$2:$D$39,D26,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3494,7 +3516,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,C27)+1)/2)/COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$39,D27,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$39,D27,$C$2:$C$39,C27)+1)/2)/COUNTIFS($D$2:$D$39,D27,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3505,7 +3527,10 @@
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="30" t="n"/>
+      <c r="J27" s="30">
+        <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K27" s="30" t="n"/>
       <c r="L27" s="30" t="n"/>
     </row>
@@ -3533,7 +3558,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,C28)+1)/2)/COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$39,D28,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$39,D28,$C$2:$C$39,C28)+1)/2)/COUNTIFS($D$2:$D$39,D28,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3572,7 +3597,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,C29)+1)/2)/COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$39,D29,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$39,D29,$C$2:$C$39,C29)+1)/2)/COUNTIFS($D$2:$D$39,D29,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3611,7 +3636,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,C30)+1)/2)/COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$39,D30,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$39,D30,$C$2:$C$39,C30)+1)/2)/COUNTIFS($D$2:$D$39,D30,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3650,7 +3675,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,C31)+1)/2)/COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$39,D31,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$39,D31,$C$2:$C$39,C31)+1)/2)/COUNTIFS($D$2:$D$39,D31,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3689,7 +3714,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,C32)+1)/2)/COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$39,D32,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$39,D32,$C$2:$C$39,C32)+1)/2)/COUNTIFS($D$2:$D$39,D32,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3728,7 +3753,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,C33)+1)/2)/COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$39,D33,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$39,D33,$C$2:$C$39,C33)+1)/2)/COUNTIFS($D$2:$D$39,D33,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3767,7 +3792,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,C34)+1)/2)/COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$39,D34,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$39,D34,$C$2:$C$39,C34)+1)/2)/COUNTIFS($D$2:$D$39,D34,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3806,14 +3831,17 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,C35)+1)/2)/COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$39,D35,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$39,D35,$C$2:$C$39,C35)+1)/2)/COUNTIFS($D$2:$D$39,D35,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="30" t="n"/>
+      <c r="I35" s="30">
+        <f>IFERROR(B39/B35-1,"")</f>
+        <v/>
+      </c>
       <c r="J35" s="30" t="n"/>
       <c r="K35" s="30" t="n"/>
       <c r="L35" s="30" t="n"/>
@@ -3842,7 +3870,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,C36)+1)/2)/COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$39,D36,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$39,D36,$C$2:$C$39,C36)+1)/2)/COUNTIFS($D$2:$D$39,D36,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3878,7 +3906,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,C37)+1)/2)/COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$39,D37,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$39,D37,$C$2:$C$39,C37)+1)/2)/COUNTIFS($D$2:$D$39,D37,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3914,7 +3942,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,C38)+1)/2)/COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$39,D38,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$39,D38,$C$2:$C$39,C38)+1)/2)/COUNTIFS($D$2:$D$39,D38,$C$2:$C$39,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -3925,6 +3953,42 @@
       <c r="J38" s="30" t="n"/>
       <c r="K38" s="30" t="n"/>
       <c r="L38" s="30" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B39" s="24" t="n">
+        <v>30904.45</v>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E39" s="33">
+        <f>IFERROR(B39/C39,"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="30">
+        <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="30">
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$39,D39,$C$2:$C$39,"&gt;0",$C$2:$C$39,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$39,D39,$C$2:$C$39,C39)+1)/2)/COUNTIFS($D$2:$D$39,D39,$C$2:$C$39,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I39" s="30" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3939,15 +4003,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4261,6 +4325,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>30904.45</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.65671641791</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.00132301557257</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4301,7 +4398,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30904.45</v>
+        <v>30532.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.25</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6567164179104478</v>
+        <v>0.6194029850746269</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1329.223655913979</v>
+        <v>1329.229429690901</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.001323015572568531</v>
+        <v>0.001474084944902199</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04301075268817205</v>
+        <v>0.043535045711798</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>34.32835820895522</v>
+        <v>38.05970149253731</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>20.52920622902741</v>
+        <v>20.58963397796088</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>30.18861261497688</v>
+        <v>32.81868123816439</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23939.31804301076</v>
+        <v>23939.42202873313</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2253763440860214</v>
+        <v>-0.215933826730518</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29573297381295</v>
+        <v>22.29863868528309</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29636.01569473349</v>
+        <v>29640.00678252231</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.04104374306180858</v>
+        <v>-0.02922774552533347</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4358,6 +4358,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>30532.4</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.0014740849449</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4398,7 +4431,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30532.4</v>
+        <v>30700.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.97</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1329.229429690901</v>
+        <v>1329.582070160242</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.001474084944902199</v>
+        <v>0.001733924813174692</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.043535045711798</v>
+        <v>0.04330879168471199</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>20.58963397796088</v>
+        <v>20.69356992526988</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>32.81868123816439</v>
+        <v>32.84986202235709</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23939.42202873313</v>
+        <v>23945.77308358597</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.215933826730518</v>
+        <v>-0.2200086617583369</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29863868528309</v>
+        <v>22.30363651954941</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29640.00678252231</v>
+        <v>29654.51521576408</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.02922774552533347</v>
+        <v>-0.03405645216329989</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4391,6 +4391,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>30700.05</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.00173392481317</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4431,7 +4464,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30700.05</v>
+        <v>30980.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.09</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6194029850746269</v>
+        <v>0.6791044776119403</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1329.582070160242</v>
+        <v>1329.654506437768</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.001733924813174692</v>
+        <v>0.001530271402719885</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04330879168471199</v>
+        <v>0.04291845493562232</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.05970149253731</v>
+        <v>32.08955223880597</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>20.69356992526988</v>
+        <v>20.61210856108795</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>32.84986202235709</v>
+        <v>28.64631913549056</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23945.77308358597</v>
+        <v>23947.07766094421</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2200086617583369</v>
+        <v>-0.227038626609442</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.30363651954941</v>
+        <v>22.29971939166603</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29654.51521576408</v>
+        <v>29650.92238142643</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.03405645216329989</v>
+        <v>-0.04293049821175832</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4424,6 +4424,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>30980.95</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.679104477612</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.00153027140272</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4464,7 +4497,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30980.95</v>
+        <v>30672.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.3</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6791044776119403</v>
+        <v>0.6194029850746269</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1329.654506437768</v>
+        <v>1329.527524924144</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.001530271402719885</v>
+        <v>0.001560854342340434</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04291845493562232</v>
+        <v>0.04334633723450369</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>32.08955223880597</v>
+        <v>38.05970149253731</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>20.61210856108795</v>
+        <v>20.62434173693617</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>28.64631913549056</v>
+        <v>32.82909356585697</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23947.07766094421</v>
+        <v>23944.79072388383</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.227038626609442</v>
+        <v>-0.2193324664065885</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29971939166603</v>
+        <v>22.30030763266468</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29650.92238142643</v>
+        <v>29648.87281190366</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.04293049821175832</v>
+        <v>-0.03336334492134041</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4457,6 +4457,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>30672.2</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.00156085434234</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4497,7 +4530,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30672.2</v>
+        <v>30092.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.07</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6194029850746269</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1329.527524924144</v>
+        <v>1329.180653710247</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.001560854342340434</v>
+        <v>0.001147115998973769</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04334633723450369</v>
+        <v>0.0441696113074205</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.05970149253731</v>
+        <v>44.02985074626866</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>20.62434173693617</v>
+        <v>20.45884639958951</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>32.82909356585697</v>
+        <v>36.95854944226492</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23944.79072388383</v>
+        <v>23938.54357332156</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2193324664065885</v>
+        <v>-0.2045053003533569</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.30030763266468</v>
+        <v>22.29234967115741</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29648.87281190366</v>
+        <v>29630.55990864642</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.03336334492134041</v>
+        <v>-0.01535557989587444</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4490,6 +4490,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>30092.65</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.00114711599897</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4530,7 +4563,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30092.65</v>
+        <v>30516.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.64</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5597014925373134</v>
+        <v>0.6194029850746269</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1329.180653710247</v>
+        <v>1329.109320557491</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.001147115998973769</v>
+        <v>0.001348989928907862</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0441696113074205</v>
+        <v>0.04355400696864111</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>44.02985074626866</v>
+        <v>38.05970149253731</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>20.45884639958951</v>
+        <v>20.53959597156314</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>36.95854944226492</v>
+        <v>32.80366983624506</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23938.54357332156</v>
+        <v>23937.25886324042</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2045053003533569</v>
+        <v>-0.2155923344947734</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29234967115741</v>
+        <v>22.29623257200402</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29630.55990864642</v>
+        <v>29634.13052476807</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.01535557989587444</v>
+        <v>-0.0289097311844938</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4523,6 +4523,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>30516.35</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.00134898992891</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4563,7 +4596,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30516.35</v>
+        <v>30372.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.96</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6194029850746269</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1329.109320557491</v>
+        <v>1330.950920245399</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.001348989928907862</v>
+        <v>0.002579427704002768</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04355400696864111</v>
+        <v>0.04382120946538125</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.05970149253731</v>
+        <v>44.02985074626866</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>20.53959597156314</v>
+        <v>21.03177108160111</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>32.80366983624506</v>
+        <v>37.1304268468684</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>18.01</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23937.25886324042</v>
+        <v>23970.42607361963</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2155923344947734</v>
+        <v>-0.2107800175284837</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29623257200402</v>
+        <v>22.31989916372385</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29634.13052476807</v>
+        <v>29706.69033174276</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.0289097311844938</v>
+        <v>-0.02191502350026964</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4556,6 +4556,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>30372.3</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.002579427704</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4596,7 +4629,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30372.3</v>
+        <v>30876.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.82</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5597014925373134</v>
+        <v>0.6492537313432836</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1330.950920245399</v>
+        <v>1332.587397496763</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.002579427704002768</v>
+        <v>0.003602278789344382</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04382120946538125</v>
+        <v>0.04315925766076823</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>44.02985074626866</v>
+        <v>35.07462686567165</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>21.03177108160111</v>
+        <v>21.44091151573775</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>37.1304268468684</v>
+        <v>30.98451226069148</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.01</v>
+        <v>18.01517719772755</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23970.42607361963</v>
+        <v>24006.79809736279</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2107800175284837</v>
+        <v>-0.22247832551888</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.31989916372385</v>
+        <v>22.33957297374248</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29706.69033174276</v>
+        <v>29769.43341026851</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.02191502350026964</v>
+        <v>-0.03584061399471417</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4589,6 +4589,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>30876.05</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.649253731343</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.00360227878934</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4629,7 +4662,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30876.05</v>
+        <v>30752.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.17</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6492537313432836</v>
+        <v>0.6194029850746269</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1332.587397496763</v>
+        <v>1332.44150779896</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.003602278789344382</v>
+        <v>0.003677951113146616</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04315925766076823</v>
+        <v>0.04332755632582323</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>35.07462686567165</v>
+        <v>38.05970149253731</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>21.44091151573775</v>
+        <v>21.47118044525865</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>30.98451226069148</v>
+        <v>33.08314517835372</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.01517719772755</v>
+        <v>18.01586214036128</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24006.79809736279</v>
+        <v>24005.08251460119</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.22247832551888</v>
+        <v>-0.2194167183552304</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.33957297374248</v>
+        <v>22.34102847683915</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29769.43341026851</v>
+        <v>29768.11366945906</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.03584061399471417</v>
+        <v>-0.03201783029293104</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4622,6 +4622,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>30752.75</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.00367795111315</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4662,7 +4695,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30752.75</v>
+        <v>31051.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.08</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6194029850746269</v>
+        <v>0.6791044776119403</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1332.44150779896</v>
+        <v>1332.665236051502</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.003677951113146616</v>
+        <v>0.00391801400210201</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04332755632582323</v>
+        <v>0.04291845493562232</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.05970149253731</v>
+        <v>32.08955223880597</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>21.47118044525865</v>
+        <v>21.5672056008408</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>33.08314517835372</v>
+        <v>28.93284824741642</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.01586214036128</v>
+        <v>18.01803505245331</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24005.08251460119</v>
+        <v>24012.00893636193</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2194167183552304</v>
+        <v>-0.2266937745728191</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.34102847683915</v>
+        <v>22.34564591503472</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29768.11366945906</v>
+        <v>29779.26548808302</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.03201783029293104</v>
+        <v>-0.04095940278820975</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4655,6 +4655,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>31051.1</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.679104477612</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.0039180140021</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4695,7 +4728,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31051.1</v>
+        <v>31199.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.3</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1332.665236051502</v>
+        <v>1333.894826849081</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.00391801400210201</v>
+        <v>0.007435296768515398</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04291845493562232</v>
+        <v>0.04275331338178709</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>21.5672056008408</v>
+        <v>22.97411870740616</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>28.93284824741642</v>
+        <v>29.35492217938603</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.01803505245331</v>
+        <v>18.04987148617902</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24012.00893636193</v>
+        <v>24076.63020070493</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2266937745728191</v>
+        <v>-0.2283081878504052</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.34564591503472</v>
+        <v>22.41329833670185</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29779.26548808302</v>
+        <v>29896.9827039517</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.04095940278820975</v>
+        <v>-0.04175723229149864</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4688,6 +4688,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>31199.8</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.679104477612</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.00743529676852</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4728,7 +4761,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31199.8</v>
+        <v>30908.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.39</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6791044776119403</v>
+        <v>0.6194029850746269</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1333.894826849081</v>
+        <v>1339.765929778934</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.007435296768515398</v>
+        <v>0.01180638073494533</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04275331338178709</v>
+        <v>0.04334633723450369</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>32.08955223880597</v>
+        <v>38.05970149253731</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>22.97411870740616</v>
+        <v>24.72255229397813</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>29.35492217938603</v>
+        <v>34.05855673296956</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.04987148617902</v>
+        <v>18.08943604048087</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24076.63020070493</v>
+        <v>24235.61009595141</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2283081878504052</v>
+        <v>-0.2158892050073311</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.41329833670185</v>
+        <v>22.48622642292428</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29896.9827039517</v>
+        <v>30126.28005072877</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.04175723229149864</v>
+        <v>-0.02530444634051676</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4721,6 +4721,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>30908.4</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.0118063807349</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4761,7 +4794,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30908.4</v>
+        <v>30743.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.07</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1339.765929778934</v>
+        <v>1340.156931124673</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01180638073494533</v>
+        <v>0.007571245828946305</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04334633723450369</v>
+        <v>0.04359197907585004</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>24.72255229397813</v>
+        <v>23.02849833157852</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>34.05855673296956</v>
+        <v>33.55034054424968</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.08943604048087</v>
+        <v>18.05110201938886</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24235.61009595141</v>
+        <v>24191.30948572257</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2158892050073311</v>
+        <v>-0.2131167384747662</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.48622642292428</v>
+        <v>22.41591321977276</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30126.28005072877</v>
+        <v>30040.84146896765</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.02530444634051676</v>
+        <v>-0.02284597995759541</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4754,6 +4754,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>30743.2</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.00757124582895</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4794,7 +4827,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30743.2</v>
+        <v>30563.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.94</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6194029850746269</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1340.156931124673</v>
+        <v>1341.685689201053</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.007571245828946305</v>
+        <v>0.008720613223029972</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04359197907585004</v>
+        <v>0.04389815627743635</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.05970149253731</v>
+        <v>44.02985074626866</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>23.02849833157852</v>
+        <v>23.48824528921199</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>33.55034054424968</v>
+        <v>37.86736910915166</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.05110201938886</v>
+        <v>18.06150543625874</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24191.30948572257</v>
+        <v>24232.86336925538</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2131167384747662</v>
+        <v>-0.2071332117533475</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.41591321977276</v>
+        <v>22.43802048062125</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30040.84146896765</v>
+        <v>30104.77097284968</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.02284597995759541</v>
+        <v>-0.0150122703853709</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4787,6 +4787,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>30563.6</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.008720613223029999</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4827,7 +4860,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30563.6</v>
+        <v>30366.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.78</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1341.685689201053</v>
+        <v>1341.884666372072</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.008720613223029972</v>
+        <v>0.009105088865059452</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04389815627743635</v>
+        <v>0.04418912947414936</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>23.48824528921199</v>
+        <v>23.64203554602378</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>37.86736910915166</v>
+        <v>37.9135061861952</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.06150543625874</v>
+        <v>18.06498549007003</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24232.86336925538</v>
+        <v>24241.12702735894</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2071332117533475</v>
+        <v>-0.2017240172306661</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.43802048062125</v>
+        <v>22.44541559497023</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30104.77097284968</v>
+        <v>30119.15901723914</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.0150122703853709</v>
+        <v>-0.008156624172769411</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4820,6 +4820,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>30366.85</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.00910508886506</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4860,7 +4893,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30366.85</v>
+        <v>30618.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.63</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1341.884666372072</v>
+        <v>1342.32573432705</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.009105088865059452</v>
+        <v>0.009397688188653719</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04418912947414936</v>
+        <v>0.04384042086804034</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>23.64203554602378</v>
+        <v>23.75907527546149</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>37.9135061861952</v>
+        <v>37.94861810502651</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.06498549007003</v>
+        <v>18.06763393194759</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24241.12702735894</v>
+        <v>24252.64998525387</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2017240172306661</v>
+        <v>-0.2079073243337313</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.44541559497023</v>
+        <v>22.45079799655768</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30119.15901723914</v>
+        <v>30136.28390695755</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.008156624172769411</v>
+        <v>-0.01574756700755431</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4853,6 +4853,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>30618.45</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.00939768818865</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4893,7 +4926,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30618.45</v>
+        <v>30711.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.81</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1342.32573432705</v>
+        <v>1352.92731277533</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.009397688188653719</v>
+        <v>0.01776675504616376</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04384042086804034</v>
+        <v>0.04405286343612335</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>23.75907527546149</v>
+        <v>27.1067020184655</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>37.94861810502651</v>
+        <v>38.95290612792772</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.06763393194759</v>
+        <v>18.19677188563569</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24252.64998525387</v>
+        <v>24618.90968841878</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2079073243337313</v>
+        <v>-0.198380093143802</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.45079799655768</v>
+        <v>22.57389501422186</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30136.28390695755</v>
+        <v>30540.83912046361</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.01574756700755431</v>
+        <v>-0.005555285717098846</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4886,6 +4886,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>30711.45</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.0177667550462</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4926,7 +4959,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30711.45</v>
+        <v>30727</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1352.92731277533</v>
+        <v>1353.612334801762</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01776675504616376</v>
+        <v>0.0183609555647033</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>27.1067020184655</v>
+        <v>27.34438222588132</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>38.95290612792772</v>
+        <v>39.02421019015246</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.19677188563569</v>
+        <v>18.20752861273703</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24618.90968841878</v>
+        <v>24645.93531645686</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.198380093143802</v>
+        <v>-0.1979062285137873</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.57389501422186</v>
+        <v>22.58243217383848</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30540.83912046361</v>
+        <v>30567.85874033195</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.005555285717098846</v>
+        <v>-0.005179199390375033</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4919,6 +4919,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>30727</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.559701492537</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.0183609555647</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4959,7 +4992,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30727</v>
+        <v>31041.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.7</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.5597014925373134</v>
+        <v>0.6119402985074627</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1353.612334801762</v>
+        <v>1353.770170082861</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0183609555647033</v>
+        <v>0.01857604276845781</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04405286343612335</v>
+        <v>0.04361098996947231</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>44.02985074626866</v>
+        <v>38.80597014925373</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>27.34438222588132</v>
+        <v>27.43041710738312</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>39.02421019015246</v>
+        <v>35.39330423669255</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.20752861273703</v>
+        <v>18.21142230565985</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24645.93531645686</v>
+        <v>24654.08027218394</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1979062285137873</v>
+        <v>-0.205781844498044</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.58243217383848</v>
+        <v>22.59338110882651</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30567.85874033195</v>
+        <v>30586.24538644296</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.005179199390375033</v>
+        <v>-0.01468028308650204</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4952,6 +4952,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>31041.95</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.611940298507</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.0185760427685</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4992,7 +5025,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty50-equal-weight.xlsx
+++ b/docs/downloads/indices/nifty50-equal-weight.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31041.95</v>
+        <v>31194.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.93</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6119402985074627</v>
+        <v>0.6194029850746269</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1353.770170082861</v>
+        <v>1350.993936769164</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.01857604276845781</v>
+        <v>0.0165971804241436</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04361098996947231</v>
+        <v>0.04330879168471199</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.80597014925373</v>
+        <v>38.05970149253731</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>27.43041710738312</v>
+        <v>26.63887216965744</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>35.39330423669255</v>
+        <v>34.63345269567336</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>18.21142230565985</v>
+        <v>18.17559924333535</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24654.08027218394</v>
+        <v>24555.12437489227</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.205781844498044</v>
+        <v>-0.2128367586255802</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.59338110882651</v>
+        <v>22.55669224235283</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>30586.24538644296</v>
+        <v>30473.95445298672</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.01468028308650204</v>
+        <v>-0.02309691457978202</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4985,6 +4985,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>31194.45</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.619402985075</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.0165971804241</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5025,7 +5058,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
